--- a/questionnaire_templates/027_human_behavior_survey--questionnaire_templates.xlsx
+++ b/questionnaire_templates/027_human_behavior_survey--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,12 +437,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E28"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="31" customWidth="1" min="2" max="2"/>
-    <col width="31" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -525,7 +525,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Human Behavior Survey</t>
+          <t>Introduction</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -607,17 +607,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>note</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>survey_conclusion</t>
+          <t>routines_description</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Survey Conclusion</t>
+          <t>Routines Description</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -630,17 +630,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_multiple</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>email_address</t>
+          <t>stressors</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Email Address</t>
+          <t>Stressors</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
@@ -658,12 +658,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>phone_number</t>
+          <t>email_address</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Phone Number</t>
+          <t>Email Address</t>
         </is>
       </c>
       <c r="D10" t="inlineStr"/>
@@ -676,17 +676,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>date</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>date_of_birth</t>
+          <t>phone_number</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Date of Birth</t>
+          <t>Phone Number</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
@@ -699,17 +699,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>time</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>time_of_day</t>
+          <t>date_of_birth</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Time of Day</t>
+          <t>Date of Birth</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
@@ -722,17 +722,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>time</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>routines_description</t>
+          <t>time_of_day</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Routines Description</t>
+          <t>Time of Day</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
@@ -745,17 +745,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>stressors</t>
+          <t>survey_conclusion</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Stressors</t>
+          <t>Survey Conclusion</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>work_life_balance_description</t>
+          <t>contact_information</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Work-Life Balance Description</t>
+          <t>Contact Information</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -796,292 +796,16 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>email_error</t>
+          <t>additional_information</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Email</t>
+          <t>Additional Information</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>phone_error</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Phone</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>date</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>date_of_birth_error</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Date of Birth</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>time</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>time_error</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Time</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>routines_error</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Routines</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>select_multiple</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>stressors_error</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Stressors</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>work_life_balance_error</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Work-Life Balance</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>error</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Error</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>error2</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Error 2</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>error3</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Error 3</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>error4</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Error 4</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>error5</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Error 5</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>text</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>error6</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Error 6</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -1098,7 +822,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -1373,108 +1097,6 @@
         </is>
       </c>
       <c r="C16" t="inlineStr">
-        <is>
-          <t>Other</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>stressors_error_choices</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>work</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Work</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>stressors_error_choices</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>relationships</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Relationships</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>stressors_error_choices</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>personal_issues</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Personal issues</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>stressors_error_choices</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>health</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Health</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>stressors_error_choices</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>finances</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Finances</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>stressors_error_choices</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
         <is>
           <t>Other</t>
         </is>
